--- a/outputs/Lumpy/Lumpy - High N_d_report.xlsx
+++ b/outputs/Lumpy/Lumpy - High N_d_report.xlsx
@@ -511,13 +511,13 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2.040132673281823</v>
+        <v>2.275501955546905</v>
       </c>
       <c r="E4" t="n">
-        <v>1.561236677516829</v>
+        <v>1.467202178320312</v>
       </c>
       <c r="F4" t="n">
-        <v>8.326672684688674e-17</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="5">
@@ -532,16 +532,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.2765957487176496</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.237043083450296</v>
+        <v>2.796540503465152</v>
       </c>
       <c r="E5" t="n">
-        <v>1.761194801309795</v>
+        <v>1.530408153270058</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1160109998998525</v>
+        <v>-23</v>
       </c>
     </row>
     <row r="6">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.2210911089200832</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.697121319557467</v>
+        <v>2.982254789179438</v>
       </c>
       <c r="E6" t="n">
-        <v>1.942597805051574</v>
+        <v>1.808513351945984</v>
       </c>
       <c r="F6" t="n">
-        <v>-10.21360942798811</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="7">
@@ -580,16 +580,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.212151031416284</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.71175706420182</v>
+        <v>2.610826217750867</v>
       </c>
       <c r="E7" t="n">
-        <v>1.535149705133882</v>
+        <v>1.336041263753711</v>
       </c>
       <c r="F7" t="n">
-        <v>5.496845935632428</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="8">
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.1909359282746556</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.684182007132287</v>
+        <v>2.610826217750867</v>
       </c>
       <c r="E8" t="n">
-        <v>1.539981873183219</v>
+        <v>1.336041263753711</v>
       </c>
       <c r="F8" t="n">
-        <v>6.247161342069185</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="9">
@@ -628,16 +628,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.1057959987092304</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.928180246212104</v>
+        <v>2.610826217750867</v>
       </c>
       <c r="E9" t="n">
-        <v>1.311067957704384</v>
+        <v>1.336041263753711</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.926579065048655</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="10">
@@ -700,16 +700,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.851017316017316</v>
+        <v>1.789989177489177</v>
       </c>
       <c r="E12" t="n">
-        <v>1.454982156908832</v>
+        <v>1.272145707399392</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1999999999999998</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="13">
@@ -724,16 +724,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.2631817920107914</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.210955527511018</v>
+        <v>2.056655844155844</v>
       </c>
       <c r="E13" t="n">
-        <v>1.767711418750515</v>
+        <v>1.555329272308325</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2779512656050042</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="14">
@@ -748,16 +748,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.2922499538152353</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.293751214023392</v>
+        <v>2.356655844155844</v>
       </c>
       <c r="E14" t="n">
-        <v>1.909612798729108</v>
+        <v>1.905844586985935</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.089557745355909</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="15">
@@ -772,16 +772,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.5797231351459017</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.881006904990753</v>
+        <v>1.741179653679654</v>
       </c>
       <c r="E15" t="n">
-        <v>1.536067595923643</v>
+        <v>1.211470287052165</v>
       </c>
       <c r="F15" t="n">
-        <v>6.321665039640792</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -796,16 +796,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.5217508216313115</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.861477643063107</v>
+        <v>1.741179653679654</v>
       </c>
       <c r="E16" t="n">
-        <v>1.546805746588809</v>
+        <v>1.211470287052165</v>
       </c>
       <c r="F16" t="n">
-        <v>6.989498535676712</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -820,16 +820,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.7363340624199682</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.840467134887785</v>
+        <v>1.753084415584415</v>
       </c>
       <c r="E17" t="n">
-        <v>1.260467082844442</v>
+        <v>1.218329562588433</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.009913937788932</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="18">
@@ -892,16 +892,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4764705882352941</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4479310235235581</v>
+        <v>0.4977011372483979</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.7</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="21">
@@ -916,16 +916,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3.249999863730891</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>1.617102381006567</v>
+        <v>1.546840958605664</v>
       </c>
       <c r="E21" t="n">
-        <v>1.768724149646355</v>
+        <v>1.686870407085978</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.749999782145154</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="22">
@@ -940,16 +940,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5.499998209525862</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.545751836663147</v>
+        <v>1.516339869281046</v>
       </c>
       <c r="E22" t="n">
-        <v>1.656559528658931</v>
+        <v>1.641957510056763</v>
       </c>
       <c r="F22" t="n">
-        <v>-14.49999089123112</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="23">
@@ -964,16 +964,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2.170731707317073</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>1.059788865862515</v>
+        <v>0.9694989106753814</v>
       </c>
       <c r="E23" t="n">
-        <v>1.467276674070212</v>
+        <v>1.366135746306366</v>
       </c>
       <c r="F23" t="n">
-        <v>6.995934959349593</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -988,16 +988,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.953658536585366</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>1.046402571868856</v>
+        <v>1.080610021786492</v>
       </c>
       <c r="E24" t="n">
-        <v>1.490114851812347</v>
+        <v>1.556239837843643</v>
       </c>
       <c r="F24" t="n">
-        <v>7.596341463414634</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
@@ -1012,16 +1012,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.56</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>1.113115468409586</v>
+        <v>1.124183006535947</v>
       </c>
       <c r="E25" t="n">
-        <v>1.265428226597646</v>
+        <v>1.270218743954109</v>
       </c>
       <c r="F25" t="n">
-        <v>2.239999999999999</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
